--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_44.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3762670.894734367</v>
+        <v>3799028.941041583</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117101763</v>
+        <v>603.5370116961572</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117101763</v>
+        <v>603.5370116961572</v>
       </c>
     </row>
     <row r="11">
@@ -672,7 +672,7 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T2" t="n">
         <v>184.8805867536895</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -745,7 +745,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -787,13 +787,13 @@
         <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>128.8457579034114</v>
+        <v>109.1885932307311</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>374</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -909,7 +909,7 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.798687867826661</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>85.50414770182039</v>
@@ -970,28 +970,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>223.1080406939611</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
         <v>133.6519859716245</v>
@@ -1027,7 +1027,7 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>357.8161811331573</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1146,10 +1146,10 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>5.608919435675552</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132.0068113193051</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -1225,10 +1225,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>143.7261718927485</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>142.3350019731772</v>
@@ -1422,7 +1422,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U11" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1444,16 +1444,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>18.63624233787687</v>
@@ -1492,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>305.4120422616786</v>
+        <v>305.4120422616788</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
@@ -1507,10 +1507,10 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
         <v>78.39139276613435</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1574,7 +1574,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C15" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>21.67209722191262</v>
@@ -1702,7 +1702,7 @@
         <v>4.021973978873973</v>
       </c>
       <c r="I15" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1735,22 +1735,22 @@
         <v>131.8202263797057</v>
       </c>
       <c r="T15" t="n">
-        <v>402.3753501231742</v>
+        <v>254.9671660051471</v>
       </c>
       <c r="U15" t="n">
-        <v>382.1025822036413</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V15" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1808,10 +1808,10 @@
         <v>352.895266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>376.871685410242</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
         <v>40.09991244551929</v>
@@ -1936,7 +1936,7 @@
         <v>3.99961134672543</v>
       </c>
       <c r="H18" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1963,16 +1963,16 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>501.333570877285</v>
+        <v>353.9253867592582</v>
       </c>
       <c r="S18" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T18" t="n">
-        <v>176.3386178958001</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U18" t="n">
         <v>79.16168051490371</v>
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S20" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T20" t="n">
         <v>259.6218731858503</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>158.5198244189524</v>
+        <v>237.1483725282995</v>
       </c>
       <c r="C21" t="n">
         <v>40.09991244551929</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>180.333570877285</v>
@@ -2331,7 +2331,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T23" t="n">
         <v>259.6218731858503</v>
@@ -2398,13 +2398,13 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>3.999611346725456</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>180.333570877285</v>
+        <v>353.9253867592579</v>
       </c>
       <c r="S24" t="n">
         <v>131.8202263797056</v>
@@ -2449,16 +2449,16 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>193.8260072180132</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
         <v>78.39139276613435</v>
@@ -2565,10 +2565,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H26" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S26" t="n">
         <v>142.3350019731772</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
         <v>40.09991244551929</v>
@@ -2641,13 +2641,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H27" t="n">
-        <v>4.021973978873973</v>
+        <v>177.6137898608473</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2674,19 +2674,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T27" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490371</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2695,10 +2695,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>193.826007218013</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2738,25 +2738,25 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N28" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O28" t="n">
         <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S28" t="n">
         <v>30.56285675203577</v>
@@ -2808,7 +2808,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>142.3350019731772</v>
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>192.2280582198497</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2926,13 +2926,13 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V30" t="n">
-        <v>93.51066719152016</v>
+        <v>267.1024830734933</v>
       </c>
       <c r="W30" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>78.39139276613435</v>
@@ -2975,13 +2975,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N31" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O31" t="n">
         <v>231.765039488851</v>
@@ -3039,13 +3039,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H32" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3103,28 +3103,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>237.1483725282997</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3151,16 +3151,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>180.333570877285</v>
+        <v>483.2744725660227</v>
       </c>
       <c r="S33" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T33" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M34" t="n">
         <v>102.3923982877958</v>
@@ -3224,16 +3224,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P34" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q34" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S34" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H35" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3349,19 +3349,19 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F36" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H36" t="n">
-        <v>98.9852417515</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3388,19 +3388,19 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T36" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V36" t="n">
-        <v>93.51066719152016</v>
+        <v>317.8230207709107</v>
       </c>
       <c r="W36" t="n">
         <v>111.3731429098285</v>
@@ -3409,7 +3409,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,16 +3461,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090246937</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H38" t="n">
         <v>72.84688483418068</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>142.3350019731772</v>
@@ -3555,7 +3555,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U38" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V38" t="n">
         <v>308.8510241668239</v>
@@ -3589,13 +3589,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F39" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H39" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,16 +3625,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>353.9253867592579</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
-        <v>452.8202263797057</v>
+        <v>305.4120422616786</v>
       </c>
       <c r="T39" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V39" t="n">
         <v>414.5106671915202</v>
@@ -3643,10 +3643,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M40" t="n">
         <v>102.3923982877958</v>
@@ -3698,16 +3698,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P40" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q40" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090247658</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H41" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3814,13 +3814,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
         <v>21.67209722191262</v>
@@ -3829,10 +3829,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490372</v>
+        <v>252.7534963968771</v>
       </c>
       <c r="V42" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>206.3364106824542</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>78.39139276613435</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S43" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090251439</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -4054,10 +4054,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>213.6917283274924</v>
+        <v>213.6917283274923</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
         <v>21.67209722191262</v>
@@ -4102,25 +4102,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4181,7 +4181,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090252711</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4321,25 +4321,25 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L2" t="n">
-        <v>464.2419149748744</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M2" t="n">
-        <v>834.5019149748744</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N2" t="n">
-        <v>1204.761914974874</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O2" t="n">
-        <v>1204.761914974874</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P2" t="n">
-        <v>1262.853806841132</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="3">
@@ -4376,16 +4376,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>719.1203429896864</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="C3" t="n">
-        <v>719.1203429896864</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="D3" t="n">
-        <v>719.1203429896864</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="E3" t="n">
-        <v>372.9869114524009</v>
+        <v>29.92</v>
       </c>
       <c r="F3" t="n">
         <v>29.92</v>
@@ -4430,22 +4430,22 @@
         <v>1294.664012937232</v>
       </c>
       <c r="T3" t="n">
-        <v>1164.516782731766</v>
+        <v>1184.372504623362</v>
       </c>
       <c r="U3" t="n">
-        <v>1164.31887788538</v>
+        <v>806.5947268455845</v>
       </c>
       <c r="V3" t="n">
-        <v>1149.661638297986</v>
+        <v>428.8169490678068</v>
       </c>
       <c r="W3" t="n">
-        <v>1116.961493944623</v>
+        <v>396.1168047144446</v>
       </c>
       <c r="X3" t="n">
-        <v>1096.898120767464</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="Y3" t="n">
-        <v>1096.898120767464</v>
+        <v>376.0534315372855</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>141.6773376662921</v>
+        <v>1061.814541362355</v>
       </c>
       <c r="C4" t="n">
-        <v>267.679343484728</v>
+        <v>1187.816547180791</v>
       </c>
       <c r="D4" t="n">
-        <v>380.998487609728</v>
+        <v>1301.135691305791</v>
       </c>
       <c r="E4" t="n">
-        <v>498.8273918211411</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="F4" t="n">
-        <v>498.8273918211411</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="G4" t="n">
-        <v>498.8273918211411</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="H4" t="n">
-        <v>669.9629678002108</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="I4" t="n">
-        <v>896.5719424739987</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J4" t="n">
-        <v>1255.222976822941</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K4" t="n">
         <v>1386.743548464727</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U4" t="n">
-        <v>29.92</v>
+        <v>316.9048008472139</v>
       </c>
       <c r="V4" t="n">
-        <v>29.92</v>
+        <v>515.7261937331598</v>
       </c>
       <c r="W4" t="n">
-        <v>29.92</v>
+        <v>687.6171119928372</v>
       </c>
       <c r="X4" t="n">
-        <v>29.92</v>
+        <v>838.6479030170307</v>
       </c>
       <c r="Y4" t="n">
-        <v>29.92</v>
+        <v>950.057203696063</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C5" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D5" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
         <v>29.92</v>
@@ -4558,52 +4558,52 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K5" t="n">
-        <v>770.4399999999999</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L5" t="n">
-        <v>834.5019149748742</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M5" t="n">
-        <v>834.5019149748744</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.648108133742</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1314.492137192891</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
       </c>
       <c r="R5" t="n">
-        <v>1494.183143567852</v>
+        <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W5" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>466.9711646468727</v>
+        <v>714.7552206300469</v>
       </c>
       <c r="C6" t="n">
-        <v>466.9711646468727</v>
+        <v>714.7552206300469</v>
       </c>
       <c r="D6" t="n">
-        <v>466.9711646468727</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="E6" t="n">
-        <v>466.9711646468727</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="F6" t="n">
-        <v>241.6095073802453</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="G6" t="n">
-        <v>241.6095073802453</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="H6" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1357.784024336592</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>1294.664012937232</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T6" t="n">
-        <v>1290.14538216673</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U6" t="n">
-        <v>1289.947477320344</v>
+        <v>782.1759777479623</v>
       </c>
       <c r="V6" t="n">
-        <v>1275.29023773295</v>
+        <v>767.5187381605682</v>
       </c>
       <c r="W6" t="n">
-        <v>1242.590093379587</v>
+        <v>734.8185938072061</v>
       </c>
       <c r="X6" t="n">
-        <v>1222.526720202428</v>
+        <v>714.7552206300469</v>
       </c>
       <c r="Y6" t="n">
-        <v>844.7489424246505</v>
+        <v>714.7552206300469</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>905.2325217179426</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="C7" t="n">
-        <v>1031.234527536378</v>
+        <v>385.1994033501023</v>
       </c>
       <c r="D7" t="n">
-        <v>1144.553671661379</v>
+        <v>385.1994033501023</v>
       </c>
       <c r="E7" t="n">
-        <v>1262.382575872791</v>
+        <v>503.0283075615154</v>
       </c>
       <c r="F7" t="n">
-        <v>1386.743548464727</v>
+        <v>627.3892801534508</v>
       </c>
       <c r="G7" t="n">
-        <v>1386.743548464727</v>
+        <v>780.9779411223033</v>
       </c>
       <c r="H7" t="n">
-        <v>1386.743548464727</v>
+        <v>952.113517101373</v>
       </c>
       <c r="I7" t="n">
-        <v>1386.743548464727</v>
+        <v>1178.722491775161</v>
       </c>
       <c r="J7" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4752,16 +4752,16 @@
         <v>259.1973975316665</v>
       </c>
       <c r="V7" t="n">
-        <v>359.1441740887474</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="W7" t="n">
-        <v>531.0350923484248</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="X7" t="n">
-        <v>682.0658833726183</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="Y7" t="n">
-        <v>793.4751840516506</v>
+        <v>259.1973975316665</v>
       </c>
     </row>
     <row r="8">
@@ -4789,31 +4789,31 @@
         <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>400.18</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
+        <v>515.8802453266331</v>
+      </c>
+      <c r="M8" t="n">
         <v>697.388108133742</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1067.648108133742</v>
       </c>
-      <c r="N8" t="n">
-        <v>1437.908108133742</v>
-      </c>
       <c r="O8" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P8" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1089.186506748585</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="C9" t="n">
-        <v>724.4391204399794</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="D9" t="n">
-        <v>372.9869114524009</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="E9" t="n">
-        <v>372.9869114524009</v>
+        <v>729.8543702394629</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>386.787458787062</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>386.787458787062</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1357.784024336592</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.664012937232</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T9" t="n">
-        <v>1290.14538216673</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U9" t="n">
-        <v>1289.947477320344</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V9" t="n">
-        <v>1275.29023773295</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W9" t="n">
-        <v>1242.590093379587</v>
+        <v>1096.051174953908</v>
       </c>
       <c r="X9" t="n">
-        <v>1222.526720202428</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y9" t="n">
-        <v>1222.526720202428</v>
+        <v>1075.987801776748</v>
       </c>
     </row>
     <row r="10">
@@ -4929,25 +4929,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1250.668263144111</v>
+        <v>404.1174293695179</v>
       </c>
       <c r="C10" t="n">
-        <v>1376.670268962547</v>
+        <v>530.1194351879536</v>
       </c>
       <c r="D10" t="n">
-        <v>1386.743548464727</v>
+        <v>643.4385793129537</v>
       </c>
       <c r="E10" t="n">
-        <v>1386.743548464727</v>
+        <v>761.2674835243668</v>
       </c>
       <c r="F10" t="n">
-        <v>1386.743548464727</v>
+        <v>885.6284561163022</v>
       </c>
       <c r="G10" t="n">
-        <v>1386.743548464727</v>
+        <v>1039.217117085155</v>
       </c>
       <c r="H10" t="n">
-        <v>1386.743548464727</v>
+        <v>1210.352693064224</v>
       </c>
       <c r="I10" t="n">
         <v>1386.743548464727</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>505.7585226289696</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>704.5799155149155</v>
+        <v>29.92</v>
       </c>
       <c r="W10" t="n">
-        <v>876.4708337745928</v>
+        <v>29.92</v>
       </c>
       <c r="X10" t="n">
-        <v>1027.501624798786</v>
+        <v>180.9507910241935</v>
       </c>
       <c r="Y10" t="n">
-        <v>1138.910925477819</v>
+        <v>292.3600917032257</v>
       </c>
     </row>
     <row r="11">
@@ -5032,37 +5032,37 @@
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L11" t="n">
-        <v>949.6332762537361</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M11" t="n">
-        <v>1114.38799366138</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N11" t="n">
-        <v>1756.89799366138</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O11" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P11" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
       </c>
       <c r="R11" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S11" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U11" t="n">
         <v>1858.092802114017</v>
@@ -5093,7 +5093,7 @@
         <v>452.1903149324157</v>
       </c>
       <c r="D12" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E12" t="n">
         <v>78.84709864997603</v>
@@ -5135,28 +5135,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R12" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S12" t="n">
-        <v>1753.535205884734</v>
+        <v>1429.292781642309</v>
       </c>
       <c r="T12" t="n">
-        <v>1671.337882527992</v>
+        <v>1347.095458285568</v>
       </c>
       <c r="U12" t="n">
-        <v>1591.376589078594</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V12" t="n">
-        <v>1496.92136969322</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W12" t="n">
-        <v>1384.423245541878</v>
+        <v>735.9383970570298</v>
       </c>
       <c r="X12" t="n">
-        <v>960.319468324315</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y12" t="n">
-        <v>881.1362433080177</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="13">
@@ -5196,25 +5196,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M13" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R13" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5272,13 +5272,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K14" t="n">
-        <v>737.2059437357115</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L14" t="n">
-        <v>953.2578922784251</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M14" t="n">
-        <v>1595.767892278425</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N14" t="n">
         <v>2238.277892278425</v>
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>362.0396347695416</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C15" t="n">
-        <v>321.5346727033605</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D15" t="n">
-        <v>294.3248879582063</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E15" t="n">
-        <v>272.4338806633451</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F15" t="n">
-        <v>253.6093934533685</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G15" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H15" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I15" t="n">
         <v>51.92</v>
@@ -5378,22 +5378,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1522.440726853217</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U15" t="n">
-        <v>1136.478522607115</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V15" t="n">
-        <v>1042.023303221741</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W15" t="n">
-        <v>929.5251790703987</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X15" t="n">
-        <v>829.6638260952598</v>
+        <v>960.319468324315</v>
       </c>
       <c r="Y15" t="n">
-        <v>426.2381768365382</v>
+        <v>881.1362433080177</v>
       </c>
     </row>
     <row r="16">
@@ -5451,7 +5451,7 @@
         <v>463.4700425881595</v>
       </c>
       <c r="R16" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C17" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D17" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E17" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F17" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G17" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
@@ -5530,28 +5530,28 @@
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X17" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>844.5079366300614</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C18" t="n">
-        <v>804.0029745638803</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D18" t="n">
-        <v>452.5507655763019</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E18" t="n">
-        <v>430.6597582814406</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F18" t="n">
-        <v>411.835271071464</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G18" t="n">
-        <v>407.7952596101252</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H18" t="n">
-        <v>403.7326596314647</v>
+        <v>51.92</v>
       </c>
       <c r="I18" t="n">
-        <v>403.7326596314647</v>
+        <v>51.92</v>
       </c>
       <c r="J18" t="n">
-        <v>596.8967549011032</v>
+        <v>245.0840952696386</v>
       </c>
       <c r="K18" t="n">
-        <v>904.3763400520904</v>
+        <v>552.5636804206258</v>
       </c>
       <c r="L18" t="n">
-        <v>1334.777960137857</v>
+        <v>982.9653005063919</v>
       </c>
       <c r="M18" t="n">
-        <v>1606.463701880716</v>
+        <v>1254.651042249251</v>
       </c>
       <c r="N18" t="n">
-        <v>1930.261603846775</v>
+        <v>1578.44894421531</v>
       </c>
       <c r="O18" t="n">
-        <v>2343.590454775776</v>
+        <v>1991.777795144312</v>
       </c>
       <c r="P18" t="n">
-        <v>2596</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="Q18" t="n">
-        <v>2516.577224131972</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R18" t="n">
-        <v>2010.17967779128</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S18" t="n">
-        <v>1552.785509730972</v>
+        <v>1753.535205884733</v>
       </c>
       <c r="T18" t="n">
-        <v>1374.665693674608</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U18" t="n">
-        <v>1294.70440022521</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V18" t="n">
-        <v>1200.249180839836</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W18" t="n">
-        <v>1087.751056688494</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X18" t="n">
-        <v>987.8897037133553</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y18" t="n">
-        <v>908.7064786970579</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="19">
@@ -5746,19 +5746,19 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L20" t="n">
-        <v>523.631587033441</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M20" t="n">
-        <v>1166.141587033441</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N20" t="n">
-        <v>1792.359898617045</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O20" t="n">
-        <v>1953.49</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P20" t="n">
         <v>2596</v>
@@ -5767,7 +5767,7 @@
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S20" t="n">
         <v>2451.762030971221</v>
@@ -5843,31 +5843,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R21" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S21" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T21" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U21" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V21" t="n">
-        <v>1592.843862392842</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W21" t="n">
-        <v>1480.3457382415</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X21" t="n">
-        <v>1380.484385266361</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y21" t="n">
-        <v>1301.301160250064</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="22">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D23" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H23" t="n">
         <v>51.92</v>
@@ -5983,19 +5983,19 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K23" t="n">
-        <v>307.5796384907274</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L23" t="n">
-        <v>523.631587033441</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M23" t="n">
-        <v>1166.141587033441</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N23" t="n">
-        <v>1792.359898617045</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O23" t="n">
-        <v>1953.49</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P23" t="n">
         <v>2596</v>
@@ -6007,25 +6007,25 @@
         <v>2596</v>
       </c>
       <c r="S23" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W23" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X23" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.4528527561725</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C24" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D24" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E24" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F24" t="n">
         <v>60.02261143999941</v>
@@ -6080,31 +6080,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q24" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R24" t="n">
-        <v>1982.60944240224</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S24" t="n">
-        <v>1849.457698584356</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T24" t="n">
-        <v>1767.260375227614</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U24" t="n">
-        <v>1363.056657535792</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V24" t="n">
-        <v>944.3590139079936</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W24" t="n">
-        <v>507.6184655142274</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X24" t="n">
-        <v>311.8346198394665</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.6513948231691</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="25">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D26" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H26" t="n">
         <v>51.92</v>
@@ -6217,52 +6217,52 @@
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>733.5813277110226</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L26" t="n">
-        <v>949.6332762537361</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M26" t="n">
-        <v>949.6332762537362</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N26" t="n">
-        <v>949.6332762537362</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O26" t="n">
-        <v>1367.045081027735</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P26" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q26" t="n">
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S26" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W26" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>492.6952769985969</v>
+        <v>343.7981213238225</v>
       </c>
       <c r="C27" t="n">
-        <v>452.1903149324158</v>
+        <v>303.2931592576414</v>
       </c>
       <c r="D27" t="n">
-        <v>424.9805301872616</v>
+        <v>276.0833745124872</v>
       </c>
       <c r="E27" t="n">
-        <v>403.0895228924003</v>
+        <v>254.192367217626</v>
       </c>
       <c r="F27" t="n">
-        <v>60.0226114399994</v>
+        <v>235.3678800076493</v>
       </c>
       <c r="G27" t="n">
-        <v>55.98259997866058</v>
+        <v>231.3278685463105</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6317,31 +6317,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q27" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R27" t="n">
-        <v>1982.60944240224</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S27" t="n">
-        <v>1849.457698584356</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T27" t="n">
-        <v>1767.260375227614</v>
+        <v>1198.198302610793</v>
       </c>
       <c r="U27" t="n">
-        <v>1687.299081778216</v>
+        <v>793.9945849189712</v>
       </c>
       <c r="V27" t="n">
-        <v>1592.843862392842</v>
+        <v>699.5393655335973</v>
       </c>
       <c r="W27" t="n">
-        <v>1480.3457382415</v>
+        <v>587.0412413822554</v>
       </c>
       <c r="X27" t="n">
-        <v>1284.56189256674</v>
+        <v>487.1798884071164</v>
       </c>
       <c r="Y27" t="n">
-        <v>881.1362433080178</v>
+        <v>407.9966633908191</v>
       </c>
     </row>
     <row r="28">
@@ -6381,10 +6381,10 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M28" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N28" t="n">
         <v>1349.248439584877</v>
@@ -6396,7 +6396,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R28" t="n">
         <v>82.79157247680381</v>
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C29" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D29" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E29" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H29" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I29" t="n">
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K29" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L29" t="n">
-        <v>1009.32297330616</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M29" t="n">
-        <v>1651.83297330616</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N29" t="n">
-        <v>1651.83297330616</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="O29" t="n">
-        <v>1812.963074689115</v>
+        <v>2395.783377636692</v>
       </c>
       <c r="P29" t="n">
-        <v>2009.555081027735</v>
+        <v>2592.375383975311</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>992.2829698086705</v>
+        <v>816.9377012410209</v>
       </c>
       <c r="C30" t="n">
-        <v>951.7780077424894</v>
+        <v>776.4327391748399</v>
       </c>
       <c r="D30" t="n">
-        <v>600.3257987549109</v>
+        <v>749.2229544296857</v>
       </c>
       <c r="E30" t="n">
-        <v>254.1923672176254</v>
+        <v>727.3319471348245</v>
       </c>
       <c r="F30" t="n">
-        <v>60.0226114399994</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866058</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6569,16 +6569,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>1672.26663826087</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W30" t="n">
-        <v>1559.768514109528</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X30" t="n">
-        <v>1459.907161134389</v>
+        <v>960.3194683243148</v>
       </c>
       <c r="Y30" t="n">
-        <v>1380.723936118091</v>
+        <v>881.1362433080175</v>
       </c>
     </row>
     <row r="31">
@@ -6618,10 +6618,10 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M31" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N31" t="n">
         <v>1349.248439584877</v>
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D32" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F32" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H32" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I32" t="n">
         <v>51.92</v>
@@ -6703,13 +6703,13 @@
         <v>1592.599638490728</v>
       </c>
       <c r="N32" t="n">
-        <v>1651.83297330616</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O32" t="n">
-        <v>1812.963074689115</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P32" t="n">
-        <v>2009.555081027735</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6727,16 +6727,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W32" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="33">
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1141.180125483445</v>
+        <v>686.2820590119658</v>
       </c>
       <c r="C33" t="n">
-        <v>776.43273917484</v>
+        <v>645.7770969457847</v>
       </c>
       <c r="D33" t="n">
-        <v>424.9805301872615</v>
+        <v>618.5673122006306</v>
       </c>
       <c r="E33" t="n">
-        <v>78.84709864997603</v>
+        <v>596.6763049057694</v>
       </c>
       <c r="F33" t="n">
-        <v>60.02261143999941</v>
+        <v>253.6093934533685</v>
       </c>
       <c r="G33" t="n">
-        <v>55.98259997866057</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H33" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I33" t="n">
         <v>51.92</v>
@@ -6794,28 +6794,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R33" t="n">
-        <v>2062.032218270268</v>
+        <v>1756.031307473563</v>
       </c>
       <c r="S33" t="n">
-        <v>1928.880474452383</v>
+        <v>1298.637139413254</v>
       </c>
       <c r="T33" t="n">
-        <v>1846.683151095642</v>
+        <v>1216.439816056512</v>
       </c>
       <c r="U33" t="n">
-        <v>1766.721857646244</v>
+        <v>1136.478522607115</v>
       </c>
       <c r="V33" t="n">
-        <v>1672.26663826087</v>
+        <v>1042.023303221741</v>
       </c>
       <c r="W33" t="n">
-        <v>1559.768514109528</v>
+        <v>929.5251790703986</v>
       </c>
       <c r="X33" t="n">
-        <v>1459.907161134389</v>
+        <v>829.6638260952597</v>
       </c>
       <c r="Y33" t="n">
-        <v>1380.723936118092</v>
+        <v>750.4806010789623</v>
       </c>
     </row>
     <row r="34">
@@ -6855,25 +6855,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L34" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M34" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N34" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O34" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P34" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R34" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C35" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D35" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E35" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F35" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G35" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H35" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
@@ -6934,19 +6934,19 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L35" t="n">
-        <v>1418.446838088717</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M35" t="n">
-        <v>1595.767892278425</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N35" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O35" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P35" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
@@ -6964,16 +6964,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W35" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X35" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="36">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>588.617769698219</v>
+        <v>686.2820590119658</v>
       </c>
       <c r="C36" t="n">
-        <v>548.112807632038</v>
+        <v>645.7770969457847</v>
       </c>
       <c r="D36" t="n">
-        <v>520.9030228868838</v>
+        <v>618.5673122006306</v>
       </c>
       <c r="E36" t="n">
-        <v>174.7695913495983</v>
+        <v>596.6763049057694</v>
       </c>
       <c r="F36" t="n">
-        <v>155.9451041396217</v>
+        <v>253.6093934533685</v>
       </c>
       <c r="G36" t="n">
-        <v>151.9050926782828</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H36" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I36" t="n">
         <v>51.92</v>
@@ -7031,7 +7031,7 @@
         <v>2164.764564500508</v>
       </c>
       <c r="R36" t="n">
-        <v>1658.367018159816</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S36" t="n">
         <v>1525.215274341931</v>
@@ -7043,16 +7043,16 @@
         <v>1363.056657535792</v>
       </c>
       <c r="V36" t="n">
-        <v>1268.601438150418</v>
+        <v>1042.023303221741</v>
       </c>
       <c r="W36" t="n">
-        <v>1156.103313999076</v>
+        <v>929.5251790703986</v>
       </c>
       <c r="X36" t="n">
-        <v>1056.241961023937</v>
+        <v>829.6638260952597</v>
       </c>
       <c r="Y36" t="n">
-        <v>652.8163117652156</v>
+        <v>750.4806010789623</v>
       </c>
     </row>
     <row r="37">
@@ -7077,40 +7077,40 @@
         <v>855.3151236491811</v>
       </c>
       <c r="G37" t="n">
-        <v>931.1258141262304</v>
+        <v>931.1258141262615</v>
       </c>
       <c r="H37" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.892525187298</v>
       </c>
       <c r="I37" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.283805434857</v>
       </c>
       <c r="J37" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611898</v>
       </c>
       <c r="K37" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024177</v>
       </c>
       <c r="L37" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405787</v>
       </c>
       <c r="M37" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.22798246862</v>
       </c>
       <c r="N37" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605517</v>
       </c>
       <c r="O37" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111728</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645525</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881908</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949744382</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7153,7 +7153,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F38" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G38" t="n">
         <v>125.5027119537179</v>
@@ -7165,16 +7165,16 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K38" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L38" t="n">
-        <v>949.6332762537361</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M38" t="n">
-        <v>1592.143276253736</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N38" t="n">
         <v>1651.83297330616</v>
@@ -7189,13 +7189,13 @@
         <v>2596</v>
       </c>
       <c r="R38" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S38" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T38" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U38" t="n">
         <v>1858.092802114017</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>168.4528527561725</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C39" t="n">
-        <v>127.9478906899915</v>
+        <v>452.1903149324158</v>
       </c>
       <c r="D39" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E39" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F39" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G39" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H39" t="n">
         <v>51.92</v>
@@ -7268,28 +7268,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R39" t="n">
-        <v>1886.686949702618</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S39" t="n">
-        <v>1429.292781642309</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T39" t="n">
-        <v>1347.095458285568</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U39" t="n">
-        <v>1267.13416483617</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V39" t="n">
-        <v>848.4365212083717</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W39" t="n">
-        <v>735.9383970570298</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X39" t="n">
-        <v>311.8346198394665</v>
+        <v>960.319468324315</v>
       </c>
       <c r="Y39" t="n">
-        <v>232.6513948231691</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="40">
@@ -7299,55 +7299,55 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>686.6440969023969</v>
+        <v>686.6440969024352</v>
       </c>
       <c r="C40" t="n">
-        <v>734.4361027208327</v>
+        <v>734.436102720871</v>
       </c>
       <c r="D40" t="n">
-        <v>769.5452468458327</v>
+        <v>769.545246845871</v>
       </c>
       <c r="E40" t="n">
-        <v>809.1641510572457</v>
+        <v>809.164151057284</v>
       </c>
       <c r="F40" t="n">
-        <v>855.3151236491811</v>
+        <v>855.3151236492195</v>
       </c>
       <c r="G40" t="n">
-        <v>931.1258141262304</v>
+        <v>931.1258141262687</v>
       </c>
       <c r="H40" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.892525187306</v>
       </c>
       <c r="I40" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.283805434864</v>
       </c>
       <c r="J40" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611906</v>
       </c>
       <c r="K40" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024184</v>
       </c>
       <c r="L40" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405795</v>
       </c>
       <c r="M40" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468627</v>
       </c>
       <c r="N40" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605524</v>
       </c>
       <c r="O40" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111735</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645598</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881981</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949745109</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7368,7 +7368,7 @@
         <v>619.8974585570725</v>
       </c>
       <c r="Y40" t="n">
-        <v>653.0967592361047</v>
+        <v>653.096759236143</v>
       </c>
     </row>
     <row r="41">
@@ -7378,25 +7378,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D41" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H41" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I41" t="n">
         <v>51.92</v>
@@ -7414,40 +7414,40 @@
         <v>1166.141587033441</v>
       </c>
       <c r="N41" t="n">
-        <v>1651.83297330616</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="O41" t="n">
-        <v>1812.963074689115</v>
+        <v>1953.49</v>
       </c>
       <c r="P41" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S41" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W41" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="42">
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>492.6952769985969</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C42" t="n">
-        <v>452.1903149324157</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D42" t="n">
         <v>100.7381059448373</v>
@@ -7469,10 +7469,10 @@
         <v>78.84709864997603</v>
       </c>
       <c r="F42" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H42" t="n">
         <v>51.92</v>
@@ -7502,31 +7502,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q42" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>1982.60944240224</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S42" t="n">
-        <v>1849.457698584356</v>
+        <v>1280.395625967535</v>
       </c>
       <c r="T42" t="n">
-        <v>1767.260375227614</v>
+        <v>1198.198302610793</v>
       </c>
       <c r="U42" t="n">
-        <v>1687.299081778216</v>
+        <v>942.8917405937455</v>
       </c>
       <c r="V42" t="n">
-        <v>1592.843862392842</v>
+        <v>524.1940969659473</v>
       </c>
       <c r="W42" t="n">
-        <v>1384.423245541878</v>
+        <v>411.6959728146054</v>
       </c>
       <c r="X42" t="n">
-        <v>960.319468324315</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y42" t="n">
-        <v>881.1362433080177</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="43">
@@ -7560,31 +7560,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J43" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611944</v>
       </c>
       <c r="K43" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024222</v>
       </c>
       <c r="L43" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405833</v>
       </c>
       <c r="M43" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468665</v>
       </c>
       <c r="N43" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605563</v>
       </c>
       <c r="O43" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111774</v>
       </c>
       <c r="P43" t="n">
-        <v>820.7766206439126</v>
+        <v>819.929907664598</v>
       </c>
       <c r="Q43" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425882363</v>
       </c>
       <c r="R43" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949748929</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7651,13 +7651,13 @@
         <v>1166.141587033441</v>
       </c>
       <c r="N44" t="n">
-        <v>1808.651587033441</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O44" t="n">
-        <v>1969.781688416396</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P44" t="n">
-        <v>2166.373694755016</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>668.0405455662465</v>
+        <v>343.798121323822</v>
       </c>
       <c r="C45" t="n">
-        <v>452.1903149324157</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D45" t="n">
         <v>100.7381059448373</v>
@@ -7745,25 +7745,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S45" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T45" t="n">
-        <v>1846.683151095642</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U45" t="n">
-        <v>1766.721857646244</v>
+        <v>1118.237009161395</v>
       </c>
       <c r="V45" t="n">
-        <v>1672.26663826087</v>
+        <v>1023.781789776021</v>
       </c>
       <c r="W45" t="n">
-        <v>1235.526089867104</v>
+        <v>911.2836656246792</v>
       </c>
       <c r="X45" t="n">
-        <v>811.4223126495403</v>
+        <v>811.4223126495402</v>
       </c>
       <c r="Y45" t="n">
-        <v>732.239087633243</v>
+        <v>407.9966633908186</v>
       </c>
     </row>
     <row r="46">
@@ -7773,55 +7773,55 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>686.6440969023969</v>
+        <v>686.6440969024865</v>
       </c>
       <c r="C46" t="n">
-        <v>734.4361027208327</v>
+        <v>734.4361027209222</v>
       </c>
       <c r="D46" t="n">
-        <v>769.5452468458327</v>
+        <v>769.5452468459223</v>
       </c>
       <c r="E46" t="n">
-        <v>809.1641510572457</v>
+        <v>809.1641510573353</v>
       </c>
       <c r="F46" t="n">
-        <v>855.3151236491811</v>
+        <v>855.3151236492707</v>
       </c>
       <c r="G46" t="n">
-        <v>931.1258141262304</v>
+        <v>931.1258141263199</v>
       </c>
       <c r="H46" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.892525187357</v>
       </c>
       <c r="I46" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.283805434915</v>
       </c>
       <c r="J46" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611957</v>
       </c>
       <c r="K46" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024235</v>
       </c>
       <c r="L46" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405845</v>
       </c>
       <c r="M46" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468678</v>
       </c>
       <c r="N46" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605575</v>
       </c>
       <c r="O46" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111786</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076646108</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425882492</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949750214</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7833,16 +7833,16 @@
         <v>332.7843563872555</v>
       </c>
       <c r="V46" t="n">
-        <v>453.3957492732014</v>
+        <v>453.3957492732911</v>
       </c>
       <c r="W46" t="n">
-        <v>547.0766675328789</v>
+        <v>547.0766675329685</v>
       </c>
       <c r="X46" t="n">
-        <v>619.8974585570725</v>
+        <v>619.8974585571621</v>
       </c>
       <c r="Y46" t="n">
-        <v>653.0967592361047</v>
+        <v>653.0967592361943</v>
       </c>
     </row>
   </sheetData>
@@ -7964,10 +7964,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="Q2" t="n">
-        <v>364.0430754681111</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>472.2608914614128</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>639.5838718235262</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>311.8831458198699</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,16 +8438,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>655.6021670241489</v>
       </c>
       <c r="N8" t="n">
         <v>778.0826666125488</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.5418702571336</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8684,19 +8684,19 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>467.8533356222227</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>879.4920535472222</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O11" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,16 +8915,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>433.9659648939233</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M14" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N14" t="n">
-        <v>879.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9389,22 +9389,22 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N20" t="n">
-        <v>863.0358026215699</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>23.48346824708341</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9635,13 +9635,13 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>863.0358026215699</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>23.48346824708341</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O26" t="n">
-        <v>258.8704074657004</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>17.50927946942295</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>27.14469655484982</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10346,7 +10346,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
-        <v>290.3237048759414</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10577,13 +10577,13 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L35" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>480.5466050990546</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>879.4920535472222</v>
+        <v>248.0013330166451</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,7 +10808,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N38" t="n">
-        <v>290.7846768324985</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -11057,16 +11057,16 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>721.0894134186553</v>
+        <v>863.0358026215699</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11294,7 +11294,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>879.4920535472222</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>457.4494331410071</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23666,10 +23666,10 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -24596,13 +24596,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -24833,13 +24833,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495663947</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495591933</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25781,7 +25781,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.8382458495213747</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495086524</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26278,7 +26278,7 @@
         <v>1385314.744365854</v>
       </c>
       <c r="E2" t="n">
-        <v>1385292.614675425</v>
+        <v>1385292.614675426</v>
       </c>
       <c r="F2" t="n">
         <v>1385292.614675425</v>
@@ -26290,7 +26290,7 @@
         <v>1385292.614675425</v>
       </c>
       <c r="I2" t="n">
-        <v>1385292.614675425</v>
+        <v>1385292.614675426</v>
       </c>
       <c r="J2" t="n">
         <v>1385292.614675425</v>
@@ -26299,19 +26299,19 @@
         <v>1385292.614675425</v>
       </c>
       <c r="L2" t="n">
-        <v>1385292.614675426</v>
+        <v>1385292.614675425</v>
       </c>
       <c r="M2" t="n">
         <v>1385292.614675426</v>
       </c>
       <c r="N2" t="n">
-        <v>1385292.614675426</v>
+        <v>1385292.614675427</v>
       </c>
       <c r="O2" t="n">
-        <v>1385292.614675426</v>
+        <v>1385292.614675427</v>
       </c>
       <c r="P2" t="n">
-        <v>1385292.614675425</v>
+        <v>1385292.614675428</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570963.5697337884</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634526</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.979796175</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308644</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193655</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286018</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301401</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785569</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>518161.4096990892</v>
+        <v>524662.774632066</v>
       </c>
       <c r="C6" t="n">
-        <v>751268.3318865778</v>
+        <v>757769.6968195547</v>
       </c>
       <c r="D6" t="n">
-        <v>753279.9793024018</v>
+        <v>759781.3442353782</v>
       </c>
       <c r="E6" t="n">
-        <v>231859.0858792505</v>
+        <v>238322.077009605</v>
       </c>
       <c r="F6" t="n">
-        <v>823095.1486974731</v>
+        <v>829558.1398278273</v>
       </c>
       <c r="G6" t="n">
-        <v>824783.5382191262</v>
+        <v>831246.5293494806</v>
       </c>
       <c r="H6" t="n">
-        <v>826474.2711290891</v>
+        <v>832937.2622594429</v>
       </c>
       <c r="I6" t="n">
-        <v>828167.3643296363</v>
+        <v>834630.3554599907</v>
       </c>
       <c r="J6" t="n">
-        <v>441414.8349445604</v>
+        <v>447877.8260749152</v>
       </c>
       <c r="K6" t="n">
-        <v>831560.7003233943</v>
+        <v>838023.6914537483</v>
       </c>
       <c r="L6" t="n">
-        <v>833260.9780457387</v>
+        <v>839723.9691760917</v>
       </c>
       <c r="M6" t="n">
-        <v>738163.6859257064</v>
+        <v>744626.6770560605</v>
       </c>
       <c r="N6" t="n">
-        <v>836668.8420164703</v>
+        <v>843131.8331468251</v>
       </c>
       <c r="O6" t="n">
-        <v>581576.4646149325</v>
+        <v>588039.455745287</v>
       </c>
       <c r="P6" t="n">
-        <v>840086.5722665156</v>
+        <v>846549.5633968712</v>
       </c>
     </row>
   </sheetData>
@@ -26999,16 +26999,16 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>-0</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27106,7 +27106,7 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -27451,7 +27451,7 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I2" t="n">
         <v>134.2726973711268</v>
@@ -27484,7 +27484,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27524,7 +27524,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.5201396486123</v>
@@ -27566,13 +27566,13 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>275.6276865593855</v>
+        <v>295.2848512320658</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>26.1959257979226</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27600,7 +27600,7 @@
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>367.4534878257808</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
@@ -27609,16 +27609,16 @@
         <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
-        <v>384.5385569711199</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L4" t="n">
         <v>396.2015953708939</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I5" t="n">
         <v>134.2726973711268</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>223.3220918649904</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27749,28 +27749,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>116.5282016439158</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>42.37974466476533</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27828,13 +27828,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
@@ -27843,22 +27843,22 @@
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>95.73959749235519</v>
       </c>
       <c r="K7" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27888,16 +27888,16 @@
         <v>150.9483584875727</v>
       </c>
       <c r="V7" t="n">
-        <v>300.1266501728635</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27986,16 +27986,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>252.5497453270216</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -28004,10 +28004,10 @@
         <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>186.3230096332952</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28071,22 +28071,22 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>295.7112478557377</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>349.2746269966815</v>
       </c>
       <c r="J10" t="n">
         <v>22.26478490148153</v>
@@ -28116,19 +28116,19 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28201,7 +28201,7 @@
         <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V11" t="n">
         <v>321</v>
@@ -28223,16 +28223,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>321</v>
@@ -28271,10 +28271,10 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>147.4081841180271</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28286,10 +28286,10 @@
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y12" t="n">
         <v>321</v>
@@ -28460,13 +28460,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>321</v>
@@ -28481,7 +28481,7 @@
         <v>321</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28514,22 +28514,22 @@
         <v>321</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="U15" t="n">
-        <v>18.05909831126235</v>
+        <v>321</v>
       </c>
       <c r="V15" t="n">
         <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>321</v>
@@ -28715,7 +28715,7 @@
         <v>321</v>
       </c>
       <c r="H18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>191.6509141932353</v>
@@ -28742,16 +28742,16 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T18" t="n">
-        <v>226.036732227374</v>
+        <v>321</v>
       </c>
       <c r="U18" t="n">
         <v>321</v>
@@ -28903,10 +28903,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S20" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T20" t="n">
         <v>321</v>
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>226.0367322273742</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="C21" t="n">
         <v>321</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R21" t="n">
         <v>321</v>
@@ -29110,7 +29110,7 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>96.76634561233286</v>
@@ -29143,7 +29143,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S23" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T23" t="n">
         <v>321</v>
@@ -29177,13 +29177,13 @@
         <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29216,10 +29216,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R24" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="S24" t="n">
         <v>321</v>
@@ -29228,16 +29228,16 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
         <v>321</v>
@@ -29347,7 +29347,7 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I26" t="n">
         <v>96.76634561233286</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C27" t="n">
         <v>321</v>
@@ -29420,13 +29420,13 @@
         <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G27" t="n">
         <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>321</v>
+        <v>147.4081841180266</v>
       </c>
       <c r="I27" t="n">
         <v>191.6509141932353</v>
@@ -29453,19 +29453,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>321</v>
@@ -29474,10 +29474,10 @@
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>226.0367322273745</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28">
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,25 +29645,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
         <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F30" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>191.6509141932353</v>
@@ -29705,13 +29705,13 @@
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="W30" t="n">
         <v>321</v>
       </c>
       <c r="X30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>321</v>
@@ -29821,10 +29821,10 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I32" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29882,19 +29882,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29903,7 +29903,7 @@
         <v>321</v>
       </c>
       <c r="I33" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29930,10 +29930,10 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
-        <v>321</v>
+        <v>18.05909831126223</v>
       </c>
       <c r="S33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>321</v>
@@ -30058,10 +30058,10 @@
         <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I35" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30128,19 +30128,19 @@
         <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>321</v>
       </c>
       <c r="H36" t="n">
-        <v>226.036732227374</v>
+        <v>321</v>
       </c>
       <c r="I36" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30167,10 +30167,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>321</v>
@@ -30179,7 +30179,7 @@
         <v>321</v>
       </c>
       <c r="V36" t="n">
-        <v>321</v>
+        <v>96.6876464206095</v>
       </c>
       <c r="W36" t="n">
         <v>321</v>
@@ -30188,7 +30188,7 @@
         <v>321</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37">
@@ -30213,7 +30213,7 @@
         <v>321</v>
       </c>
       <c r="G37" t="n">
-        <v>321</v>
+        <v>321.0000000000314</v>
       </c>
       <c r="H37" t="n">
         <v>321</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S38" t="n">
         <v>321</v>
@@ -30334,7 +30334,7 @@
         <v>321</v>
       </c>
       <c r="U38" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V38" t="n">
         <v>321</v>
@@ -30368,7 +30368,7 @@
         <v>321</v>
       </c>
       <c r="F39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
@@ -30404,10 +30404,10 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R39" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="T39" t="n">
         <v>321</v>
@@ -30422,10 +30422,10 @@
         <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -30504,7 +30504,7 @@
         <v>321</v>
       </c>
       <c r="Y40" t="n">
-        <v>321</v>
+        <v>321.0000000000387</v>
       </c>
     </row>
     <row r="41">
@@ -30535,7 +30535,7 @@
         <v>321</v>
       </c>
       <c r="I41" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30593,13 +30593,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C42" t="n">
         <v>321</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
         <v>321</v>
@@ -30638,28 +30638,28 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>321</v>
       </c>
       <c r="U42" t="n">
-        <v>321</v>
+        <v>147.4081841180266</v>
       </c>
       <c r="V42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y42" t="n">
         <v>321</v>
@@ -30696,7 +30696,7 @@
         <v>321</v>
       </c>
       <c r="J43" t="n">
-        <v>321</v>
+        <v>321.0000000000778</v>
       </c>
       <c r="K43" t="n">
         <v>321</v>
@@ -30833,10 +30833,10 @@
         <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>147.4081841180269</v>
+        <v>147.408184118027</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
         <v>321</v>
@@ -30881,25 +30881,25 @@
         <v>321</v>
       </c>
       <c r="S45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>321</v>
       </c>
       <c r="U45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>321</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -30969,7 +30969,7 @@
         <v>321</v>
       </c>
       <c r="V46" t="n">
-        <v>321</v>
+        <v>321.0000000000906</v>
       </c>
       <c r="W46" t="n">
         <v>321</v>
@@ -34743,10 +34743,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L2" t="n">
         <v>64.70900502512563</v>
@@ -34761,10 +34761,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>242.0199542155222</v>
       </c>
       <c r="Q2" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34886,7 +34886,7 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>86.47258298882423</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -34895,16 +34895,16 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>362.2737720696383</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>52.1599296482412</v>
+      </c>
+      <c r="L5" t="n">
+        <v>64.70900502512562</v>
+      </c>
+      <c r="M5" t="n">
         <v>374</v>
       </c>
-      <c r="K5" t="n">
-        <v>373.9999999999999</v>
-      </c>
-      <c r="L5" t="n">
-        <v>64.70900502512563</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
-        <v>235.5012052109774</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="P5" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,13 +35114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
@@ -35129,22 +35129,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>73.47481259087365</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35174,16 +35174,16 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>100.9563399566473</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35217,16 +35217,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L8" t="n">
-        <v>300.210210236103</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="N8" t="n">
         <v>374</v>
@@ -35238,7 +35238,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35357,22 +35357,22 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>10.17502980018224</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>178.1725812126288</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35402,19 +35402,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35454,7 +35454,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
         <v>175.9119195979899</v>
@@ -35463,19 +35463,19 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M11" t="n">
-        <v>166.4189064723678</v>
+        <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>649</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O11" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P11" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35694,16 +35694,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K14" t="n">
-        <v>609.8778844919133</v>
+        <v>649</v>
       </c>
       <c r="L14" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M14" t="n">
         <v>649</v>
       </c>
       <c r="N14" t="n">
-        <v>649</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
@@ -36168,22 +36168,22 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M20" t="n">
+        <v>179.1121759491996</v>
+      </c>
+      <c r="N20" t="n">
         <v>649</v>
-      </c>
-      <c r="N20" t="n">
-        <v>632.5437490743477</v>
       </c>
       <c r="O20" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P20" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36405,7 +36405,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K23" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L23" t="n">
         <v>218.2342914572864</v>
@@ -36414,13 +36414,13 @@
         <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>632.5437490743477</v>
+        <v>649</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L26" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O26" t="n">
-        <v>421.6280856303014</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P26" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q26" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36791,7 +36791,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H28" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I28" t="n">
         <v>163.0214951995539</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K29" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L29" t="n">
-        <v>235.7435709267094</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
         <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -36897,7 +36897,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
-        <v>592.3686050224903</v>
+        <v>3.661228307766413</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37125,7 +37125,7 @@
         <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>59.83165132871924</v>
+        <v>649</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>592.3686050224903</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37265,7 +37265,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H34" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I34" t="n">
         <v>163.0214951995539</v>
@@ -37356,13 +37356,13 @@
         <v>649</v>
       </c>
       <c r="L35" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M35" t="n">
         <v>649</v>
       </c>
-      <c r="M35" t="n">
-        <v>179.1121759491996</v>
-      </c>
       <c r="N35" t="n">
-        <v>649</v>
+        <v>17.50927946942293</v>
       </c>
       <c r="O35" t="n">
         <v>162.757678164601</v>
@@ -37371,7 +37371,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37499,10 +37499,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G37" t="n">
-        <v>76.57645502732242</v>
+        <v>76.57645502735386</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37587,7 +37587,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K38" t="n">
         <v>175.9119195979899</v>
@@ -37599,7 +37599,7 @@
         <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>60.29262328527629</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
@@ -37739,7 +37739,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H40" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I40" t="n">
         <v>163.0214951995539</v>
@@ -37790,7 +37790,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>33.53464715053764</v>
+        <v>33.53464715057636</v>
       </c>
     </row>
     <row r="41">
@@ -37836,16 +37836,16 @@
         <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>490.5973598714331</v>
+        <v>632.5437490743477</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P41" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q41" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37976,13 +37976,13 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
       </c>
       <c r="J43" t="n">
-        <v>329.5882314919611</v>
+        <v>329.5882314920389</v>
       </c>
       <c r="K43" t="n">
         <v>104.5500458709881</v>
@@ -38073,7 +38073,7 @@
         <v>649</v>
       </c>
       <c r="N44" t="n">
-        <v>649</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
@@ -38082,7 +38082,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>433.9659648939237</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38255,7 +38255,7 @@
         <v>170.0754447911158</v>
       </c>
       <c r="V46" t="n">
-        <v>121.8296897837838</v>
+        <v>121.8296897838743</v>
       </c>
       <c r="W46" t="n">
         <v>94.62719016129032</v>
